--- a/artifacts/japan-2026-07/Russel-inventory-2026-07.xlsx
+++ b/artifacts/japan-2026-07/Russel-inventory-2026-07.xlsx
@@ -8389,7 +8389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8417,7 +8417,7 @@
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>EUGENE — 12 cards</t>
+          <t>EUGENE — 12 cards + pharmacy</t>
         </is>
       </c>
     </row>
@@ -8778,243 +8778,524 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>E7-04</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Pharmacy — furikake ×2</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>1 noritama + 1 yakiniku · Sugi Pharmacy Day 7</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>398</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F18" s="12">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="26">
-        <f>SUM(D6:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="27">
-        <f>SUM(F6:F17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="26">
+        <f>SUM(D6:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="27">
+        <f>SUM(F6:F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Two rates: 0.38 on the Day 2 Shinsoku pair, 0.385 on everything from Osaka. D6-33 and D6-34 are 50/50 — this is his half only.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>VM — 1 item</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>VM — 2 items</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>Amount ¥</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Owed ₱</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>E2-04</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>GU jeans</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>¥1,990 sticker, billed net of the 9.09% tax-free discount</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D24" s="10" t="n">
         <v>1809</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E24" s="11" t="n">
         <v>0.38</v>
       </c>
-      <c r="F23" s="12">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="F24" s="12">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>E7-03</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Kit Kat ×6</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>オトナの甘さ ×3 + 濃い抹茶 ×3 · Sugi Pharmacy Day 7</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>1710</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F25" s="12">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="26">
-        <f>SUM(D23:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="27">
-        <f>SUM(F23:F23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="26">
+        <f>SUM(D24:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="27">
+        <f>SUM(F24:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Billed on the same tax-free basis Nico and Kenshin settled on, so VM gets the benefit of the exemption.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>KIM — pharmacy basket</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Amount ¥</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Owed ₱</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Gorilla no Hitotsukami</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>ゴリラのひとつかみ歌舞 · the single largest item on the receipt</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>4878</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F31" s="12">
+        <f>D31*E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Curel milk makeup remover</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>キュレル 乳液メイク落とし · receipt line written "Kin", read as Kim</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1464</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F32" s="12">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>30 vegetables + S</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>30種類の国産野菜+S</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>1418</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F33" s="12">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Pair Acne Cream W</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>ペアアクネ クリームW</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>957</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F34" s="12">
+        <f>D34*E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Ashi-rila sheet sakura ×2</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>足リラシート 桜の香り</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>385</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F35" s="12">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Silcot sponge 40pc</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>シルコット スポンジ40枚</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>222</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F36" s="12">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="26">
+        <f>SUM(D31:D36)</f>
+        <v/>
+      </c>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="27">
+        <f>SUM(F31:F36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>All from the Sugi Pharmacy run, 2 August. Costs are net of the 3% all-item discount and the tax-free deduction, spread pro-rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>ADRIAN — 1 item</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>Amount ¥</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>FX</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>Owed ₱</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>E6-02</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>びっくりドンキー 道頓堀</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>¥1,140 order + ¥114 pro-rata share of the late-night surcharge</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D42" s="10" t="n">
         <v>1254</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E42" s="11" t="n">
         <v>0.385</v>
       </c>
-      <c r="F29" s="12">
-        <f>D29*E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="F42" s="12">
+        <f>D42*E42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="26">
-        <f>SUM(D29:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="27">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="26">
+        <f>SUM(D42:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="27">
+        <f>SUM(F42:F42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>Not requested on this tab, included because it is outstanding on the same basis.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>TOTAL OWED TO RUSSEL</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="19">
-        <f>D18+D24+D30</f>
-        <v/>
-      </c>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="20">
-        <f>F18+F24+F30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="28" t="inlineStr">
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="19">
+        <f>D19+D26+D37+D43</f>
+        <v/>
+      </c>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="20">
+        <f>F19+F26+F37+F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>Not booked: Nico's ¥2,464 share of the same Dotonbori dinner. Russel has not said whether Nico owes it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A25:F25"/>
+  <mergeCells count="5">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artifacts/japan-2026-07/Russel-inventory-2026-07.xlsx
+++ b/artifacts/japan-2026-07/Russel-inventory-2026-07.xlsx
@@ -9176,7 +9176,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>ADRIAN — 1 item</t>
+          <t>ADRIAN — SETTLED</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>びっくりドンキー 道頓堀</t>
+          <t>びっくりドンキー 道頓堀 — PAID</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -9260,25 +9260,25 @@
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>Not requested on this tab, included because it is outstanding on the same basis.</t>
+          <t>Settled. Shown for the record; excluded from the total below.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>TOTAL OWED TO RUSSEL</t>
+          <t>TOTAL STILL OWED</t>
         </is>
       </c>
       <c r="B46" s="18" t="n"/>
       <c r="C46" s="18" t="n"/>
       <c r="D46" s="19">
-        <f>D19+D26+D37+D43</f>
+        <f>D19+D26+D37</f>
         <v/>
       </c>
       <c r="E46" s="18" t="n"/>
       <c r="F46" s="20">
-        <f>F19+F26+F37+F43</f>
+        <f>F19+F26+F37</f>
         <v/>
       </c>
     </row>

--- a/artifacts/japan-2026-07/Russel-inventory-2026-07.xlsx
+++ b/artifacts/japan-2026-07/Russel-inventory-2026-07.xlsx
@@ -9026,7 +9026,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>キュレル 乳液メイク落とし · receipt line written "Kin", read as Kim</t>
+          <t>キュレル 乳液メイク落とし</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
